--- a/results/Int All Data -0.5/Rando_fi_explain.xlsx
+++ b/results/Int All Data -0.5/Rando_fi_explain.xlsx
@@ -1676,466 +1676,466 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001019846737175644</v>
+        <v>-0.001986912701807098</v>
       </c>
       <c r="C3" t="n">
-        <v>-6.163402395897854e-07</v>
+        <v>-0.000140303470848433</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0001510854021434937</v>
+        <v>-0.000310516852096735</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0001584504662262376</v>
+        <v>-0.001058553782486681</v>
       </c>
       <c r="F3" t="n">
-        <v>0.000467812088499635</v>
+        <v>0.000376969483453089</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001026666665316583</v>
+        <v>0.0008659807758921213</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0001561960368881543</v>
+        <v>-3.320647271816028e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.002162978335174293</v>
+        <v>-0.001432600885466778</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.0007366537273589879</v>
+        <v>-0.0004834743809456354</v>
       </c>
       <c r="K3" t="n">
-        <v>-6.416854124600358e-05</v>
+        <v>-4.405933186548027e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>2.45216677005311e-05</v>
+        <v>0.0001006129913066978</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0003219094211946317</v>
+        <v>0.001096132166847237</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0001655078977048475</v>
+        <v>0.0001934656686599977</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.001995702779957726</v>
+        <v>-0.001096108667458587</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0001642750426891082</v>
+        <v>-0.0007227883663053559</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003486049193782122</v>
+        <v>0.001771430594777925</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.0003799013060767809</v>
+        <v>-0.0003133438706986958</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0001076911798498158</v>
+        <v>-0.0001879343671781619</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0003309805674228106</v>
+        <v>-0.0003106030998349763</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0003821410777754408</v>
+        <v>-0.0006593097975038353</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.0001407180473750956</v>
+        <v>-0.0002916428699306486</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.001408049284283599</v>
+        <v>-0.0009501579522632709</v>
       </c>
       <c r="X3" t="n">
-        <v>0.002138354260345178</v>
+        <v>-0.001353282549167799</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.524967495938337e-05</v>
+        <v>-1.97099814008006e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.003149518335580582</v>
+        <v>0.001234986347054868</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.001338605946116671</v>
+        <v>-0.001398233133196255</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0003681319653243731</v>
+        <v>0.0001562904835211365</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.0005199550476361747</v>
+        <v>-0.001239449554422647</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.004642677958323045</v>
+        <v>0.001556511173216138</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.004469954672451607</v>
+        <v>0.006132203563472771</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.002177147565444931</v>
+        <v>-0.0009624121178554169</v>
       </c>
       <c r="AG3" t="n">
-        <v>-6.222400328813157e-05</v>
+        <v>6.426988760241726e-05</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.0005497882682590716</v>
+        <v>0.0001185680833058378</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.001360854419034141</v>
+        <v>0.002091632680199135</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.0003935971754728342</v>
+        <v>-0.002417290777306231</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.01046905344480981</v>
+        <v>0.008845675430536144</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.000551208471337249</v>
+        <v>-0.0002618888485121628</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.003347294741367039</v>
+        <v>0.002268590422827059</v>
       </c>
       <c r="AN3" t="n">
-        <v>-6.90982385058647e-05</v>
+        <v>-0.001136303283963745</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.001100086510901754</v>
+        <v>0.0001399522304110956</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.0002955788710693484</v>
+        <v>-0.0005127773953849624</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-6.193474577791071e-05</v>
+        <v>-0.001451523033629784</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.0007908819408428712</v>
+        <v>0.003114625678060891</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.0003648436314368597</v>
+        <v>6.535541504018034e-05</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.0002586455358110895</v>
+        <v>-0.0004215763261103377</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.00051308396966247</v>
+        <v>-0.0004499891445469173</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.0001028490105743295</v>
+        <v>-0.0004765096550936943</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0.0003390757566519676</v>
+        <v>-0.001299450667202919</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.992470022014305e-05</v>
+        <v>-7.659493104257272e-06</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.0006136893347073859</v>
+        <v>-0.001574671711781123</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.0003978138164639711</v>
+        <v>-0.0003085217121625439</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.002708491824096736</v>
+        <v>0.0008053656679246791</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.001346618808697311</v>
+        <v>-0.001088120779548656</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.411767713849768e-05</v>
+        <v>-9.857201905097532e-05</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.0002537110702063894</v>
+        <v>6.284107462972558e-07</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.0001900399606401193</v>
+        <v>-0.00128288434753156</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.0008689319967709873</v>
+        <v>-0.000578146547378654</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.001282271642140996</v>
+        <v>-0.001083840286121541</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.000715493533656183</v>
+        <v>0.0001280511810036822</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.004464333486903328</v>
+        <v>0.004111678932776601</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.001107720727473654</v>
+        <v>0.0003540269049222833</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.0005863397488660605</v>
+        <v>-0.001358384096625448</v>
       </c>
       <c r="BL3" t="n">
-        <v>-0.0002654377832537436</v>
+        <v>-0.0003329903249216781</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.0001843898881661043</v>
+        <v>-0.0008948721741279031</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.0009839641788752828</v>
+        <v>-0.001305389416237305</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.001824722453072209</v>
+        <v>-0.000416881476537635</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.0003490626989330469</v>
+        <v>-0.000776571113593093</v>
       </c>
       <c r="BQ3" t="n">
         <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.0007960765068757137</v>
+        <v>0.004671193703531805</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.0004428612954646538</v>
+        <v>-0.001357112796126074</v>
       </c>
       <c r="BT3" t="n">
-        <v>1.599420039151367e-05</v>
+        <v>0.0002311737570211058</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.001570688171143626</v>
+        <v>0.0002554062219087227</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.0009396789424345254</v>
+        <v>-0.001437193920131707</v>
       </c>
       <c r="BW3" t="n">
-        <v>3.661350915187489e-05</v>
+        <v>-6.386234429164416e-05</v>
       </c>
       <c r="BX3" t="n">
-        <v>8.918699721428999e-05</v>
+        <v>-0.00054684797084815</v>
       </c>
       <c r="BY3" t="n">
-        <v>-5.177192891657192e-05</v>
+        <v>-0.0003151878900332272</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-0.001320789110277003</v>
+        <v>5.386439880254558e-05</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.0002092013495723755</v>
+        <v>-5.472593082653917e-05</v>
       </c>
       <c r="CB3" t="n">
-        <v>-0.0002338763931963572</v>
+        <v>-0.0009292937838497594</v>
       </c>
       <c r="CC3" t="n">
-        <v>-0.0002544542635340353</v>
+        <v>-0.002772992875106745</v>
       </c>
       <c r="CD3" t="n">
-        <v>-0.0001470594300838058</v>
+        <v>-0.001075709495525435</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.000301194641565573</v>
+        <v>-0.0002063182289513122</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.136269426394114e-05</v>
+        <v>-0.001316035938215068</v>
       </c>
       <c r="CG3" t="n">
-        <v>-0.0001068394929594363</v>
+        <v>-0.00124309525270778</v>
       </c>
       <c r="CH3" t="n">
-        <v>-4.972179936425958e-05</v>
+        <v>-0.0009400448901386837</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0.0009919441025611621</v>
+        <v>-0.003041260979305956</v>
       </c>
       <c r="CJ3" t="n">
-        <v>-1.297574134385471e-05</v>
+        <v>-2.416426892648982e-05</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.0003887116458109463</v>
+        <v>-3.349833525812863e-05</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.0001730871294947356</v>
+        <v>-0.001820880805619086</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.0007746811957208988</v>
+        <v>0.0005142063017377007</v>
       </c>
       <c r="CN3" t="n">
-        <v>7.41505607447237e-06</v>
+        <v>-5.322085665128926e-05</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.0008004677273093818</v>
+        <v>-8.7443795220179e-05</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.0002218593879781383</v>
+        <v>-4.923209770694936e-05</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.0005644483740197225</v>
+        <v>-0.001215302603191726</v>
       </c>
       <c r="CR3" t="n">
-        <v>-0.001438917743988226</v>
+        <v>-0.002050117426223485</v>
       </c>
       <c r="CS3" t="n">
-        <v>-0.0009434346119229654</v>
+        <v>-0.001014990158196372</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0.0009130106346651956</v>
+        <v>-0.0008598374523029406</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.0001139481807122333</v>
+        <v>-0.0003141437311316897</v>
       </c>
       <c r="CV3" t="n">
-        <v>5.996304890641955e-06</v>
+        <v>-0.0002271208454544138</v>
       </c>
       <c r="CW3" t="n">
         <v>0</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0.0007341488534260111</v>
+        <v>-0.0009037005445435619</v>
       </c>
       <c r="CY3" t="n">
-        <v>-0.000932933267450796</v>
+        <v>-0.00138492548672818</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.0002186980989101384</v>
+        <v>-0.0001305035756449424</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.0001673880460718413</v>
+        <v>0.000103892742659375</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.0002843281685441878</v>
+        <v>-0.0003774398411490819</v>
       </c>
       <c r="DC3" t="n">
-        <v>-0.0005509906982064138</v>
+        <v>-0.0007522688083920636</v>
       </c>
       <c r="DD3" t="n">
-        <v>1.51227394403175e-05</v>
+        <v>-6.603754736934865e-05</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.000444510786049479</v>
+        <v>7.879824572451952e-05</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0.0006338473293299351</v>
+        <v>-0.0009417321674561128</v>
       </c>
       <c r="DG3" t="n">
-        <v>-0.0001641035946625025</v>
+        <v>-0.0002287127217050689</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.0003081319520612846</v>
+        <v>-0.001877352642507219</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.0002297873858186716</v>
+        <v>-0.0003940636839738299</v>
       </c>
       <c r="DJ3" t="n">
-        <v>-0.0007279130352505214</v>
+        <v>-8.261091115635349e-07</v>
       </c>
       <c r="DK3" t="n">
-        <v>8.72792037108627e-05</v>
+        <v>-0.0006612109195071913</v>
       </c>
       <c r="DL3" t="n">
-        <v>-5.053408334808274e-05</v>
+        <v>-5.441358304110632e-05</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.0001948620403550183</v>
+        <v>-2.845311505270012e-05</v>
       </c>
       <c r="DN3" t="n">
-        <v>-0.0004261021519975716</v>
+        <v>-0.0003565196136273253</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0.0009245130913510192</v>
+        <v>-0.002064540122628969</v>
       </c>
       <c r="DP3" t="n">
-        <v>-0.001174104093390295</v>
+        <v>-0.001656530954575005</v>
       </c>
       <c r="DQ3" t="n">
-        <v>6.536628790941857e-05</v>
+        <v>0.0001365168707014086</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.0001357777584983133</v>
+        <v>-7.729753883172319e-05</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.0001322930598489158</v>
+        <v>-0.0002530474311685183</v>
       </c>
       <c r="DT3" t="n">
-        <v>-0.0005575965283328021</v>
+        <v>-0.0002757523551085251</v>
       </c>
       <c r="DU3" t="n">
-        <v>-0.0008036438803664658</v>
+        <v>-0.001624585334528981</v>
       </c>
       <c r="DV3" t="n">
-        <v>-2.962957209597939e-06</v>
+        <v>-6.133088009812049e-06</v>
       </c>
       <c r="DW3" t="n">
-        <v>3.890495597730359e-05</v>
+        <v>0.0001709483597575656</v>
       </c>
       <c r="DX3" t="n">
-        <v>-0.0001319689832161408</v>
+        <v>-0.0002580008515285836</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.0003676078897213275</v>
+        <v>-0.0003393864460414264</v>
       </c>
       <c r="DZ3" t="n">
-        <v>1.463876217071335e-05</v>
+        <v>1.374912703809406e-05</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.0005382046757758431</v>
+        <v>-0.0001942597045520156</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0.0004869109018046658</v>
+        <v>-0.001422957221258843</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.0002045671799178195</v>
+        <v>-0.0001902358741027021</v>
       </c>
       <c r="ED3" t="n">
-        <v>-9.282916665681593e-05</v>
+        <v>-0.001087968320842481</v>
       </c>
       <c r="EE3" t="n">
-        <v>6.77310090726857e-05</v>
+        <v>2.417996745973205e-05</v>
       </c>
       <c r="EF3" t="n">
-        <v>-0.0001543755793390001</v>
+        <v>-0.0004459252729283857</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.0006726415709557821</v>
+        <v>-0.0009441517018452604</v>
       </c>
       <c r="EH3" t="n">
-        <v>-0.0001336509741880509</v>
+        <v>-0.0001460862603350588</v>
       </c>
       <c r="EI3" t="n">
-        <v>-0.0009072513568902884</v>
+        <v>-0.0004164991824917175</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.0001567422801259078</v>
+        <v>-0.0001731790143906908</v>
       </c>
       <c r="EK3" t="n">
-        <v>-8.137419791728888e-05</v>
+        <v>-0.0008818638934079004</v>
       </c>
       <c r="EL3" t="n">
-        <v>-3.146288298354616e-06</v>
+        <v>9.25361479205633e-06</v>
       </c>
       <c r="EM3" t="n">
-        <v>-3.083981036857031e-05</v>
+        <v>-4.727545828719371e-05</v>
       </c>
       <c r="EN3" t="n">
-        <v>-7.242857325784447e-05</v>
+        <v>-0.0001308932171511901</v>
       </c>
       <c r="EO3" t="n">
         <v>0</v>
       </c>
       <c r="EP3" t="n">
-        <v>5.182293475560096e-05</v>
+        <v>7.764578425503157e-05</v>
       </c>
       <c r="EQ3" t="n">
-        <v>-0.0009208187960336621</v>
+        <v>-0.0005188877104366062</v>
       </c>
       <c r="ER3" t="n">
-        <v>5.025535106806255e-05</v>
+        <v>-1.306478667094435e-05</v>
       </c>
       <c r="ES3" t="n">
-        <v>-0.0001746389701054762</v>
+        <v>-6.921481427133003e-05</v>
       </c>
       <c r="ET3" t="n">
-        <v>-0.0004231093033848554</v>
+        <v>-0.00087548871113438</v>
       </c>
       <c r="EU3" t="n">
-        <v>4.708280533543441e-05</v>
+        <v>-7.36465620858639e-05</v>
       </c>
       <c r="EV3" t="n">
-        <v>-5.474067669066218e-05</v>
+        <v>-0.000178189515308711</v>
       </c>
       <c r="EW3" t="n">
-        <v>-0.000475946735826619</v>
+        <v>-0.0007746346455250653</v>
       </c>
       <c r="EX3" t="n">
-        <v>-0.0002413701310179672</v>
+        <v>-0.000713282221962348</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0.0006744330155190892</v>
+        <v>-0.0006204893719862558</v>
       </c>
     </row>
     <row r="4">
@@ -2145,466 +2145,466 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00417232374232303</v>
+        <v>0.005615093153876194</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0007291419591494171</v>
+        <v>0.0007452226371100531</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001454799963750602</v>
+        <v>0.001077767961131019</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001443006133151667</v>
+        <v>0.002977067103818423</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0006969198321991507</v>
+        <v>0.0009358366926189325</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002305551920639865</v>
+        <v>0.001931571929153255</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001893786777478083</v>
+        <v>0.002014154387317865</v>
       </c>
       <c r="I4" t="n">
-        <v>0.006144113335533028</v>
+        <v>0.003351363669684193</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002403682518329156</v>
+        <v>0.002929875355124626</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0007093359716912554</v>
+        <v>0.0004591401176069714</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0009452280694644821</v>
+        <v>0.000421397233326658</v>
       </c>
       <c r="M4" t="n">
-        <v>0.001523047107409839</v>
+        <v>0.00104918923599747</v>
       </c>
       <c r="N4" t="n">
-        <v>0.007256806601160899</v>
+        <v>0.006404537996602945</v>
       </c>
       <c r="O4" t="n">
-        <v>0.005751231161507872</v>
+        <v>0.002827765749792355</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001326380845140245</v>
+        <v>0.0009129243893111452</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.008288403123773314</v>
+        <v>0.009269269121620285</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001136398906711218</v>
+        <v>0.0009412869186183561</v>
       </c>
       <c r="S4" t="n">
-        <v>0.003665099811289664</v>
+        <v>0.003874926108508121</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0007020066558995223</v>
+        <v>0.0007805619259499295</v>
       </c>
       <c r="U4" t="n">
-        <v>0.000861283716708816</v>
+        <v>0.001175067545489115</v>
       </c>
       <c r="V4" t="n">
-        <v>0.003939935435261723</v>
+        <v>0.003534249314299054</v>
       </c>
       <c r="W4" t="n">
-        <v>0.001619741822806345</v>
+        <v>0.002008713881769703</v>
       </c>
       <c r="X4" t="n">
-        <v>0.005037158042873635</v>
+        <v>0.003929342487113392</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0003541718189662734</v>
+        <v>0.0003673765217416301</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.005270470702954515</v>
+        <v>0.005274202371276661</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.004426015945288588</v>
+        <v>0.005808898908210587</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0007005894662911096</v>
+        <v>0.001169035104404535</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.00214850931287019</v>
+        <v>0.004083011658272536</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.007717887759062971</v>
+        <v>0.008001496200760332</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.00873921918516002</v>
+        <v>0.008741351137846014</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.003124559384672031</v>
+        <v>0.003546949914821272</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.001696661375455205</v>
+        <v>0.001145855757141231</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.001875410477308458</v>
+        <v>0.0008726819266109769</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.001932132732527649</v>
+        <v>0.003317570927214622</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.008031780883232989</v>
+        <v>0.007661993406622821</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.01311966381796935</v>
+        <v>0.01701097388815764</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.001799260117829998</v>
+        <v>0.001869413901547621</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.00642908195600671</v>
+        <v>0.007585298670894942</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.002330978666045326</v>
+        <v>0.002196054974032358</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.003279507926579989</v>
+        <v>0.004472242295199073</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.002703792951000163</v>
+        <v>0.001411075277310217</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.002730667056649325</v>
+        <v>0.006230429222774185</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.007025754534073196</v>
+        <v>0.00660858575525685</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.001684687245010895</v>
+        <v>0.002999744438643701</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.001935428790052494</v>
+        <v>0.00199852449544419</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.001604828339355183</v>
+        <v>0.001852360652173519</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.002029895514289418</v>
+        <v>0.001184718074404099</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.002641353158533254</v>
+        <v>0.003432754133156121</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.00080175797827628</v>
+        <v>0.001136896240589118</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.003059051555289273</v>
+        <v>0.002677446295786982</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.001296520640286685</v>
+        <v>0.001450193928474742</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.004298193352599213</v>
+        <v>0.004220331266721921</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.003814022967223335</v>
+        <v>0.005891529360613216</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0004548131797820225</v>
+        <v>0.0004344849232639671</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.000801969661512342</v>
+        <v>0.0005085847222920577</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.002483379930679974</v>
+        <v>0.0030311044531812</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.003735583729866649</v>
+        <v>0.006101253704151975</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.005500431614815284</v>
+        <v>0.002687345543961496</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.001847253917990791</v>
+        <v>0.001403601535777354</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.005611619060312881</v>
+        <v>0.007936638226944957</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.00243475272436641</v>
+        <v>0.002442471155712574</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.002911278134538326</v>
+        <v>0.002951794128018964</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.0008746222004599242</v>
+        <v>0.0008485828569375387</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.001231672769472377</v>
+        <v>0.00200903467255923</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.004495791497257084</v>
+        <v>0.004163761133650829</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.001903957708249859</v>
+        <v>0.001828850481448631</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.001577885206243271</v>
+        <v>0.0008454777001356279</v>
       </c>
       <c r="BQ4" t="n">
         <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.004488098272511561</v>
+        <v>0.01205515104830993</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.001910445464183614</v>
+        <v>0.004744539372877598</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.00105685404212537</v>
+        <v>0.001531828348936372</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.002932896486071651</v>
+        <v>0.003588602866314873</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.001358594861209264</v>
+        <v>0.002371216305595228</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.0001342617971072801</v>
+        <v>9.377965878425234e-05</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.0009884866446549262</v>
+        <v>0.002033342876012962</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.003492481365636745</v>
+        <v>0.002830592274532298</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.003407487527041844</v>
+        <v>0.001808903519550937</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.001721876126824322</v>
+        <v>0.001193714100045191</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.001499416653294855</v>
+        <v>0.00507248459852083</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.0020773824292447</v>
+        <v>0.007025502506336425</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.00525027227728176</v>
+        <v>0.003283366663152238</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.00237551470162595</v>
+        <v>0.002018556730403959</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.001298361971497479</v>
+        <v>0.001289298645420931</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.00147454932092732</v>
+        <v>0.00283991844617092</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.0007789629358883557</v>
+        <v>0.001578353028106842</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.002288355595175219</v>
+        <v>0.005257761621424131</v>
       </c>
       <c r="CJ4" t="n">
-        <v>7.100979114551032e-05</v>
+        <v>0.0001021109173029683</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.001729765368423989</v>
+        <v>0.002259513285604372</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.001507176494780591</v>
+        <v>0.003275545232928689</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.001947547385972052</v>
+        <v>0.0009714300978742453</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.001196081476867484</v>
+        <v>0.0010850084212172</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.002469031122177903</v>
+        <v>0.001280475818008285</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.0003230898317876161</v>
+        <v>0.0002247819920215055</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.003391258806106215</v>
+        <v>0.001901227331647834</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.00200151243247926</v>
+        <v>0.003381261497432588</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.002575214449864174</v>
+        <v>0.001884119937101282</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.00290357941186362</v>
+        <v>0.001644644453173538</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.0004800396668283357</v>
+        <v>0.0002323124351702384</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.0001847016552395429</v>
+        <v>0.0005800705953553481</v>
       </c>
       <c r="CW4" t="n">
         <v>0</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.003308081345400744</v>
+        <v>0.001534692031449773</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.002612520614250132</v>
+        <v>0.003271530592284352</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.0003586288930151633</v>
+        <v>0.0005457190870714251</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.0005851487693778698</v>
+        <v>0.0006001082003224132</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.001138539486253042</v>
+        <v>0.001685706245907616</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.003209678130086967</v>
+        <v>0.002679993367218615</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.0004150179256647229</v>
+        <v>0.0001859718743905114</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.0007799417213016932</v>
+        <v>0.001689592426978686</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.003428915947105616</v>
+        <v>0.002670647109932406</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.001541521513366092</v>
+        <v>0.0007462998066819371</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.003270580321914976</v>
+        <v>0.004907692285355391</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.001519536201609435</v>
+        <v>0.001343823385459584</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.002935761859600892</v>
+        <v>0.0008335311015987624</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.001680253770346398</v>
+        <v>0.001199615584522908</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.0002542589817436263</v>
+        <v>0.0002907947670018218</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.0009006423874656063</v>
+        <v>0.001706272043115629</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.002416542958311759</v>
+        <v>0.003190464448299056</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.001539951081019939</v>
+        <v>0.003403479117311673</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.004455200568601706</v>
+        <v>0.003112570002134401</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.0003048167434082326</v>
+        <v>0.0003491021162090195</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.0005167114718431181</v>
+        <v>0.0002560755399423308</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.0005414936469137502</v>
+        <v>0.0004070585603381791</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.00258317973752022</v>
+        <v>0.002578761720046473</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.002615215272986626</v>
+        <v>0.004807031198243953</v>
       </c>
       <c r="DV4" t="n">
-        <v>1.686054364681313e-05</v>
+        <v>1.939452720127519e-05</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.0002932887632265112</v>
+        <v>0.0005682857576508407</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.00207933071196671</v>
+        <v>0.001008444550045056</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.002937758068800105</v>
+        <v>0.002806193393043112</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.0003074823769683394</v>
+        <v>0.0001986637476102995</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.001224006150892069</v>
+        <v>0.001476438980311848</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.002788643254634218</v>
+        <v>0.004176323937436298</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.001018490955190558</v>
+        <v>0.0008673647414382758</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.001208024728710629</v>
+        <v>0.001360738215734826</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.0002310940175452071</v>
+        <v>0.0001257346204647241</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.001366693306408094</v>
+        <v>0.001004841629538824</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.001202390034335187</v>
+        <v>0.001067229942832117</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.0003302191316883868</v>
+        <v>0.0006076562982197224</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.002579379898777778</v>
+        <v>0.001376081027682649</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.001057361248105101</v>
+        <v>0.0009386660352810809</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.001354568476031711</v>
+        <v>0.001446632400795927</v>
       </c>
       <c r="EL4" t="n">
-        <v>4.411435477706208e-05</v>
+        <v>3.232946089974539e-05</v>
       </c>
       <c r="EM4" t="n">
-        <v>7.162861905705774e-05</v>
+        <v>0.0001089188883202206</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.0003186236625322941</v>
+        <v>0.0003470794824440811</v>
       </c>
       <c r="EO4" t="n">
         <v>0</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.0007064963284528299</v>
+        <v>0.0004974064384305479</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.001682892482587864</v>
+        <v>0.0009910391338475686</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.0004110449153204201</v>
+        <v>0.0002333139727929064</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.0003949336223761243</v>
+        <v>0.000174190417198093</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.001733533866647225</v>
+        <v>0.00181024056600941</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.0007291581684818003</v>
+        <v>0.001018284306280417</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.0004601542625250394</v>
+        <v>0.0002183735108724314</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.002019297775791447</v>
+        <v>0.001489447628250045</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.0005765934058977685</v>
+        <v>0.0007291710069436085</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.002359599295544522</v>
+        <v>0.001529538488222332</v>
       </c>
     </row>
     <row r="5">
@@ -2614,466 +2614,466 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.005118228075426512</v>
+        <v>-0.01632212280160441</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.0009217960154624394</v>
+        <v>-0.001665179898899771</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.002009132420091353</v>
+        <v>-0.002170035671819315</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.001834862385321145</v>
+        <v>-0.009168966574670312</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0006584854833882048</v>
+        <v>-0.001367419738406705</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.003005213124808337</v>
+        <v>-0.00186649794368875</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.00330062444246213</v>
+        <v>-0.004846862920011863</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01616784942918845</v>
+        <v>-0.008886146251157046</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.004628201172477609</v>
+        <v>-0.006654400490647016</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.001771591268585937</v>
+        <v>-0.0008917954815695905</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.001962533452274784</v>
+        <v>-0.0007305936073059627</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.002087946852261979</v>
+        <v>-5.986231667165498e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.01377118644067792</v>
+        <v>-0.01189467312348669</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.01697007096575128</v>
+        <v>-0.008299907435976538</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.003037013603290117</v>
+        <v>-0.002715211354520186</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.005590256089943823</v>
+        <v>-0.01040809870294214</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.001993040177159178</v>
+        <v>-0.001625268322600393</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.007493309545049109</v>
+        <v>-0.009287257019438411</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0005061689338816788</v>
+        <v>-0.00187277051129614</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.001937046004842558</v>
+        <v>-0.002468373958654691</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.008793582227707441</v>
+        <v>-0.009040419623572937</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.003141671606401886</v>
+        <v>-0.00438648488441018</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.006242568370986967</v>
+        <v>-0.007819687212511472</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.0005350772889417543</v>
+        <v>-0.000617093489663656</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.00652499251721046</v>
+        <v>-0.01048758049678009</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.007202133965619417</v>
+        <v>-0.01254216498006744</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.001265422334704269</v>
+        <v>-0.00175386444708685</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.003035878564857397</v>
+        <v>-0.01146887457835016</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.009248727925770805</v>
+        <v>-0.01052318668252085</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.004280618311533935</v>
+        <v>-0.008620689655172441</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.001099881093935828</v>
+        <v>-0.008382877526753907</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.001898133502056365</v>
+        <v>-0.001694411414982222</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.003574818095539401</v>
+        <v>-0.001397561700862282</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.000562148657089323</v>
+        <v>-0.001070154577883509</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.01415402914064827</v>
+        <v>-0.015179392824287</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.008292978208232382</v>
+        <v>-0.01661622276029056</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.002437574316290192</v>
+        <v>-0.003269916765755099</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.002616711269699712</v>
+        <v>-0.008021550434001767</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.004519774011299471</v>
+        <v>-0.004906470407850349</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.002783597725231957</v>
+        <v>-0.00668846611177174</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.005202140309155834</v>
+        <v>-0.002499209111040845</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.004170499846672815</v>
+        <v>-0.01717264642747621</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.00904963680387404</v>
+        <v>-0.005618311533888276</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.002179176755447887</v>
+        <v>-0.005083234244946555</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.004207021791767507</v>
+        <v>-0.003420096852300225</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.001625268322600426</v>
+        <v>-0.004756242568371039</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.001936289818863224</v>
+        <v>-0.002095181083507924</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.004753143207605015</v>
+        <v>-0.01024225697638759</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.001339421613394254</v>
+        <v>-0.0020814748736247</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.003511546978804181</v>
+        <v>-0.006422836752899163</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.001912989817957389</v>
+        <v>-0.002606562404170476</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.002663873091888647</v>
+        <v>-0.003722760290556892</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.003894510886231195</v>
+        <v>-0.009839952578541755</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.0006788028386300216</v>
+        <v>-0.0008081412750673422</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.001898133502056365</v>
+        <v>-0.0008620689655172709</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.004072817031780263</v>
+        <v>-0.007329040171726431</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.002993115833582749</v>
+        <v>-0.006431535269709521</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.01261956186362231</v>
+        <v>-0.008299907435976518</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0.001165286721864456</v>
+        <v>-0.001307966706302066</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.003560274828232379</v>
+        <v>-0.003163555836760546</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.002973535533749661</v>
+        <v>-0.00288255136461204</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0.005399568034557212</v>
+        <v>-0.007942348972707736</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0.001708320151850717</v>
+        <v>-0.001686599202698535</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.002177246243483588</v>
+        <v>-0.005887764489420399</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0.005841404358353441</v>
+        <v>-0.009624697336561749</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.001592754528419749</v>
+        <v>-0.003087167070217933</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.002545231524072366</v>
+        <v>-0.002913216804661112</v>
       </c>
       <c r="BQ5" t="n">
         <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.005599273607748123</v>
+        <v>-0.001765601217656054</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.002606562404170498</v>
+        <v>-0.01425942962281506</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0.002209443099273556</v>
+        <v>-0.002459988144635439</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0.001301452784503598</v>
+        <v>-0.009230297454768444</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.003037013603290117</v>
+        <v>-0.007646710136336665</v>
       </c>
       <c r="BW5" t="n">
-        <v>-0.0001815980629539693</v>
+        <v>-0.0002810743285446615</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.001422643746295194</v>
+        <v>-0.004564315352697079</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.006272294887039276</v>
+        <v>-0.003986080354318277</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.008485035482875613</v>
+        <v>-0.002752293577981679</v>
       </c>
       <c r="CA5" t="n">
-        <v>-0.001592754528419749</v>
+        <v>-0.002407847800237872</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0.002698558724317679</v>
+        <v>-0.01462741490340383</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.003922809237583058</v>
+        <v>-0.02226310947562096</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0.01376146788990829</v>
+        <v>-0.008446694084150618</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.003319502074688785</v>
+        <v>-0.001813856675587255</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0.002179176755447898</v>
+        <v>-0.002883472057074943</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.002269242563630769</v>
+        <v>-0.007175712971481119</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.001575505350772943</v>
+        <v>-0.002943800178412104</v>
       </c>
       <c r="CI5" t="n">
-        <v>-0.006516925023726705</v>
+        <v>-0.01631401410610239</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0.0001851280468990968</v>
+        <v>-0.0002973535533749017</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0.002594115786143669</v>
+        <v>-0.00380499405469682</v>
       </c>
       <c r="CL5" t="n">
-        <v>-0.003448275862069006</v>
+        <v>-0.007760927743086477</v>
       </c>
       <c r="CM5" t="n">
-        <v>-0.001185536455245995</v>
+        <v>-0.001170515659601446</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.001450169700709614</v>
+        <v>-0.00172786177105827</v>
       </c>
       <c r="CO5" t="n">
-        <v>-0.001556420233463029</v>
+        <v>-0.002408563782337192</v>
       </c>
       <c r="CP5" t="n">
-        <v>-6.133088009813159e-05</v>
+        <v>-0.0004684572142411025</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.005245294662141265</v>
+        <v>-0.005399568034557189</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0.004014272970562038</v>
+        <v>-0.007602514217300183</v>
       </c>
       <c r="CS5" t="n">
-        <v>-0.006898602438299195</v>
+        <v>-0.003745541022592181</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0.008206958073149029</v>
+        <v>-0.004919976289270878</v>
       </c>
       <c r="CU5" t="n">
-        <v>-0.000475624256837115</v>
+        <v>-0.0007566585956416572</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0.0002468373958654624</v>
+        <v>-0.001516503122212265</v>
       </c>
       <c r="CW5" t="n">
         <v>0</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0.009307166220636365</v>
+        <v>-0.004281891168599417</v>
       </c>
       <c r="CY5" t="n">
-        <v>-0.008028545941124043</v>
+        <v>-0.008028545941123977</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.0002394492666866199</v>
+        <v>-0.001502606562404152</v>
       </c>
       <c r="DA5" t="n">
-        <v>-0.0006746396810794142</v>
+        <v>-0.0008620689655172709</v>
       </c>
       <c r="DB5" t="n">
-        <v>-0.0009484291641967957</v>
+        <v>-0.002993115833582749</v>
       </c>
       <c r="DC5" t="n">
-        <v>-0.008742194469223951</v>
+        <v>-0.006898602438299095</v>
       </c>
       <c r="DD5" t="n">
-        <v>-0.0009436834094368685</v>
+        <v>-0.0003270889087124029</v>
       </c>
       <c r="DE5" t="n">
-        <v>-0.001018204257945043</v>
+        <v>-0.003085467448318391</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.007998810585786553</v>
+        <v>-0.005738923580136756</v>
       </c>
       <c r="DG5" t="n">
-        <v>-0.004073743681237041</v>
+        <v>-0.00187059184299293</v>
       </c>
       <c r="DH5" t="n">
-        <v>-0.005352363960749384</v>
+        <v>-0.01416716064018964</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.003329297820823207</v>
+        <v>-0.002378828426999679</v>
       </c>
       <c r="DJ5" t="n">
-        <v>-0.007972160708636534</v>
+        <v>-0.001265422334704247</v>
       </c>
       <c r="DK5" t="n">
-        <v>-0.00391854365936436</v>
+        <v>-0.00296204875038566</v>
       </c>
       <c r="DL5" t="n">
-        <v>-0.0005447941888619412</v>
+        <v>-0.0007433838834373652</v>
       </c>
       <c r="DM5" t="n">
-        <v>-0.001357605677260054</v>
+        <v>-0.003171310017783036</v>
       </c>
       <c r="DN5" t="n">
-        <v>-0.006401896858328371</v>
+        <v>-0.007350326022525167</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.003984537615224548</v>
+        <v>-0.008682723758548871</v>
       </c>
       <c r="DP5" t="n">
-        <v>-0.01284567350579844</v>
+        <v>-0.006333630686886682</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0.0004161712247324756</v>
+        <v>-0.0001265422334704169</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.0005686920083807223</v>
+        <v>-0.0006658595641646392</v>
       </c>
       <c r="DS5" t="n">
-        <v>-0.0007713668620795699</v>
+        <v>-0.001066982809721395</v>
       </c>
       <c r="DT5" t="n">
-        <v>-0.006868867082961683</v>
+        <v>-0.00380499405469682</v>
       </c>
       <c r="DU5" t="n">
-        <v>-0.005694400506168984</v>
+        <v>-0.01357439241256664</v>
       </c>
       <c r="DV5" t="n">
+        <v>-6.133088009812049e-05</v>
+      </c>
+      <c r="DW5" t="n">
+        <v>-0.0006584854833882048</v>
+      </c>
+      <c r="DX5" t="n">
+        <v>-0.001755447941888599</v>
+      </c>
+      <c r="DY5" t="n">
+        <v>-0.005364552459988126</v>
+      </c>
+      <c r="DZ5" t="n">
+        <v>-0.000273972602739736</v>
+      </c>
+      <c r="EA5" t="n">
+        <v>-0.003394014193150241</v>
+      </c>
+      <c r="EB5" t="n">
+        <v>-0.009513930053349107</v>
+      </c>
+      <c r="EC5" t="n">
+        <v>-0.001666152422091893</v>
+      </c>
+      <c r="ED5" t="n">
+        <v>-0.004443073125578489</v>
+      </c>
+      <c r="EE5" t="n">
+        <v>-0.0001784121320249521</v>
+      </c>
+      <c r="EF5" t="n">
+        <v>-0.00249702734839482</v>
+      </c>
+      <c r="EG5" t="n">
+        <v>-0.002942106928187305</v>
+      </c>
+      <c r="EH5" t="n">
+        <v>-0.00113888010123383</v>
+      </c>
+      <c r="EI5" t="n">
+        <v>-0.003448275862068995</v>
+      </c>
+      <c r="EJ5" t="n">
+        <v>-0.00253084466940845</v>
+      </c>
+      <c r="EK5" t="n">
+        <v>-0.004165381055229833</v>
+      </c>
+      <c r="EL5" t="n">
         <v>-2.972651605231968e-05</v>
       </c>
-      <c r="DW5" t="n">
-        <v>-0.0003567181926278473</v>
-      </c>
-      <c r="DX5" t="n">
-        <v>-0.005061689338816899</v>
-      </c>
-      <c r="DY5" t="n">
-        <v>-0.005779490219324224</v>
-      </c>
-      <c r="DZ5" t="n">
-        <v>-0.0006541778174249724</v>
-      </c>
-      <c r="EA5" t="n">
-        <v>-0.002720658019614075</v>
-      </c>
-      <c r="EB5" t="n">
-        <v>-0.005690574985180774</v>
-      </c>
-      <c r="EC5" t="n">
-        <v>-0.001089588377723916</v>
-      </c>
-      <c r="ED5" t="n">
-        <v>-0.00186649794368875</v>
-      </c>
-      <c r="EE5" t="n">
-        <v>-0.0001210653753026314</v>
-      </c>
-      <c r="EF5" t="n">
-        <v>-0.003068649161657733</v>
-      </c>
-      <c r="EG5" t="n">
-        <v>-0.0008026159334126425</v>
-      </c>
-      <c r="EH5" t="n">
-        <v>-0.000547945205479472</v>
-      </c>
-      <c r="EI5" t="n">
-        <v>-0.007655805124960491</v>
-      </c>
-      <c r="EJ5" t="n">
-        <v>-0.002435937994305637</v>
-      </c>
-      <c r="EK5" t="n">
-        <v>-0.001542733724159173</v>
-      </c>
-      <c r="EL5" t="n">
-        <v>-6.133088009812049e-05</v>
-      </c>
       <c r="EM5" t="n">
-        <v>-0.0001486325802615984</v>
+        <v>-0.0002159827213822796</v>
       </c>
       <c r="EN5" t="n">
-        <v>-0.0006539833531510331</v>
+        <v>-0.0005947071067499143</v>
       </c>
       <c r="EO5" t="n">
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.001043973426131029</v>
+        <v>-0.0008028545941123566</v>
       </c>
       <c r="EQ5" t="n">
-        <v>-0.003949398333847531</v>
+        <v>-0.00249702734839482</v>
       </c>
       <c r="ER5" t="n">
-        <v>-0.0004870624048706418</v>
+        <v>-0.0003163555836760423</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.001248884924174898</v>
+        <v>-0.0003679852805887229</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0.004903511546978867</v>
+        <v>-0.005461277383523588</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0.0009512485136742299</v>
+        <v>-0.001967312348668282</v>
       </c>
       <c r="EV5" t="n">
-        <v>-0.001079913606911398</v>
+        <v>-0.000564803804994074</v>
       </c>
       <c r="EW5" t="n">
-        <v>-0.005646405430422674</v>
+        <v>-0.003887688984881155</v>
       </c>
       <c r="EX5" t="n">
-        <v>-0.0009809750297265496</v>
+        <v>-0.001991676575505408</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.007065720456649149</v>
+        <v>-0.00475161987041034</v>
       </c>
     </row>
     <row r="6">
@@ -3083,466 +3083,466 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.0008270650574407734</v>
+        <v>-0.002928603195700721</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.0005761839885151693</v>
+        <v>-0.0004940349524860193</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.000776539225241038</v>
+        <v>-0.0009727883996883041</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.001141948495319742</v>
+        <v>-0.001021201278512948</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0001022510455341241</v>
+        <v>1.101422569868557e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.000467597585321855</v>
+        <v>-0.0003524160175215313</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.001734286618508421</v>
+        <v>-0.0004387182639253334</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.002106915913203383</v>
+        <v>-0.003088365131867404</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.002499691989302793</v>
+        <v>-0.001793529460125215</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0002691518533703141</v>
+        <v>-0.0001536652408648809</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.0002644962806656492</v>
+        <v>-4.599816007356538e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0009889604415823346</v>
+        <v>0.0004412481287613151</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.00395807214703329</v>
+        <v>-0.001215321240104483</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.001928594435557443</v>
+        <v>-0.00180143365964637</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.0003410950123737905</v>
+        <v>-0.001085214561554718</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.002426013973433117</v>
+        <v>-0.004886357152933845</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.0009541601471481421</v>
+        <v>-0.0007759844299274842</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0004810209487946526</v>
+        <v>-0.001503299770029337</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0002155282904858169</v>
+        <v>-0.0006744435108447632</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0006696875191373103</v>
+        <v>-0.001127410611454352</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.000980466938497568</v>
+        <v>-0.001300536865121005</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.002667818911685968</v>
+        <v>-0.001578164421152523</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.0006507164239768215</v>
+        <v>-0.002631734681465547</v>
       </c>
       <c r="Y6" t="n">
-        <v>-8.384141132928847e-05</v>
+        <v>-0.0002058902977613075</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0009312773314888723</v>
+        <v>-0.0009074145993896832</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.809927360777457e-05</v>
+        <v>-0.003453596561440203</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.000271712845831365</v>
+        <v>-0.000263174610426889</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.000328625944401198</v>
+        <v>-0.001466766935602046</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.0005109648995322597</v>
+        <v>-0.002468095308987458</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.00283068117992348</v>
+        <v>0.001895376851380526</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.0001037310884341836</v>
+        <v>-0.002831420100289367</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.001362635195108358</v>
+        <v>-0.0007166094248352517</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.001500692629829672</v>
+        <v>-0.0003062088790328765</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.0002610629138074944</v>
+        <v>0.0001042083428904966</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.00360817921002764</v>
+        <v>-0.007944422823004452</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.001757394526477318</v>
+        <v>-0.002473838198943168</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.0005791756864288788</v>
+        <v>-0.001098872267761619</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0.0006759258215056018</v>
+        <v>-0.003439963186344231</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.0008716131735230308</v>
+        <v>-0.001579481441489638</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.001247654653653529</v>
+        <v>-0.002167927990840537</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.0006956480421906053</v>
+        <v>-0.001331573192167418</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.002071328951952139</v>
+        <v>-0.002249939986874283</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.003982089780326789</v>
+        <v>-0.001195101599251488</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0.0006330810262016817</v>
+        <v>-0.001695040840726184</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0.0004317990121383119</v>
+        <v>-0.001276921527974254</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.0003621905694384447</v>
+        <v>-0.0008014244441294588</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.001557784957962974</v>
+        <v>-0.001494102163750929</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.001711643060390214</v>
+        <v>-0.001752044055387536</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.0002125131080748716</v>
+        <v>-0.0004856640546104963</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.002052387553557885</v>
+        <v>-0.003228526315082286</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.0003540651628150925</v>
+        <v>-0.001024720794809753</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0.0008128300487477396</v>
+        <v>-0.001211766129249048</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0.00174766206110111</v>
+        <v>-0.004462684225224811</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0.0001797739605740201</v>
+        <v>-0.0003214357256039802</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.0007508879426904785</v>
+        <v>-0.000248317330491607</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.001232887125192933</v>
+        <v>-0.00118844390939459</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.00191855902268778</v>
+        <v>-0.003504284893603163</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.002773752063616089</v>
+        <v>-0.000557837632986169</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.0004729782087100343</v>
+        <v>-0.0008408787642304016</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.0002753559582387238</v>
+        <v>-0.0008633089796055925</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.0002380560534372605</v>
+        <v>-0.001062084190004448</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0.0001446338115651424</v>
+        <v>-0.001937810763480102</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0.0009539884748435256</v>
+        <v>-0.0009545318566295202</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.0009269764042370231</v>
+        <v>-0.001541007422446628</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0.00106143076507495</v>
+        <v>-0.002659078251615821</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.0008147635710093942</v>
+        <v>-0.001556733379560549</v>
       </c>
       <c r="BP6" t="n">
-        <v>-0.001300348082164715</v>
+        <v>-0.0009330116075492389</v>
       </c>
       <c r="BQ6" t="n">
         <v>0</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0.0008885090342543006</v>
+        <v>-0.0008605680015365741</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0.0004752718381524606</v>
+        <v>-0.001025102254281388</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0.0005578469807265812</v>
+        <v>-0.0006912908094842879</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.0001422803143002943</v>
+        <v>-0.0001068743450325982</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.001812010183880505</v>
+        <v>-0.001495906175605888</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>-0.0001112101211826894</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0.00048706722002414</v>
+        <v>-0.001300248908686869</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.001830023920207385</v>
+        <v>-0.001640461326694662</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.002704385208426349</v>
+        <v>-0.001120222835433449</v>
       </c>
       <c r="CA6" t="n">
-        <v>-0.001116395114171201</v>
+        <v>-0.0002244308999228784</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0.0009778420450688775</v>
+        <v>-0.0002285005432841436</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0.001763703607160985</v>
+        <v>-0.002296479436463783</v>
       </c>
       <c r="CD6" t="n">
-        <v>-0.001122447788994293</v>
+        <v>-0.001724603056941548</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.002514250519567576</v>
+        <v>-0.001629353147531787</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.0007357776785421099</v>
+        <v>-0.002506659773320391</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0.001275483029336225</v>
+        <v>-0.002057614111408054</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.0003844830357770362</v>
+        <v>-0.002486060365841425</v>
       </c>
       <c r="CI6" t="n">
-        <v>-0.001608212722620697</v>
+        <v>-0.001351411862837881</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0</v>
+        <v>-2.342286071205513e-05</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0.0004739385676102659</v>
+        <v>-0.0006260273899518359</v>
       </c>
       <c r="CL6" t="n">
-        <v>-0.0003290118626572552</v>
+        <v>-0.003506638497830425</v>
       </c>
       <c r="CM6" t="n">
-        <v>-0.0002486386761905656</v>
+        <v>-4.599141613872987e-06</v>
       </c>
       <c r="CN6" t="n">
-        <v>-0.0007435497252363671</v>
+        <v>-0.0005678734392466966</v>
       </c>
       <c r="CO6" t="n">
-        <v>-0.0007301530207624862</v>
+        <v>-0.00064271799890748</v>
       </c>
       <c r="CP6" t="n">
-        <v>8.326672684688674e-18</v>
+        <v>-0.0001379944802207739</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.0006860973441320583</v>
+        <v>-0.002033067701717686</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.003122463414171106</v>
+        <v>-0.004476158623600443</v>
       </c>
       <c r="CS6" t="n">
-        <v>-0.00179524630398098</v>
+        <v>-0.00220572208738303</v>
       </c>
       <c r="CT6" t="n">
-        <v>-0.00160209485065673</v>
+        <v>-0.0009123289318268056</v>
       </c>
       <c r="CU6" t="n">
-        <v>-0.0002168685694736577</v>
+        <v>-0.0003557205218836151</v>
       </c>
       <c r="CV6" t="n">
-        <v>-0.0001267282826678373</v>
+        <v>-0.000497865321307972</v>
       </c>
       <c r="CW6" t="n">
         <v>0</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0.0008330066459895979</v>
+        <v>-0.001737847049717822</v>
       </c>
       <c r="CY6" t="n">
-        <v>-0.0009788108988049828</v>
+        <v>-0.002660472449704213</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-2.31410058623871e-05</v>
+        <v>-5.516700617220205e-05</v>
       </c>
       <c r="DA6" t="n">
-        <v>-0.0001114744351962072</v>
+        <v>-6.734510625561185e-05</v>
       </c>
       <c r="DB6" t="n">
-        <v>-0.0005756866300479002</v>
+        <v>-0.001432102329991211</v>
       </c>
       <c r="DC6" t="n">
-        <v>-0.001170037873103974</v>
+        <v>-0.001510352508140578</v>
       </c>
       <c r="DD6" t="n">
-        <v>-0.0001560708387385867</v>
+        <v>-0.0002240445670866897</v>
       </c>
       <c r="DE6" t="n">
-        <v>-1.474601895190553e-05</v>
+        <v>-0.0002032448264953274</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.001917940431921819</v>
+        <v>-0.002777395899612209</v>
       </c>
       <c r="DG6" t="n">
-        <v>-0.0003177966101694657</v>
+        <v>-0.0002681313694331388</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0.001832780827381269</v>
+        <v>-0.002729693118707438</v>
       </c>
       <c r="DI6" t="n">
-        <v>5.406153117771817e-05</v>
+        <v>-0.001276940038504204</v>
       </c>
       <c r="DJ6" t="n">
-        <v>-0.001224592200841052</v>
+        <v>-0.0003119301830392413</v>
       </c>
       <c r="DK6" t="n">
-        <v>-9.36914428482316e-05</v>
+        <v>-0.001559915229209632</v>
       </c>
       <c r="DL6" t="n">
-        <v>-0.00015611061552189</v>
+        <v>-0.0001466536554116743</v>
       </c>
       <c r="DM6" t="n">
-        <v>-0.0004529896009154433</v>
+        <v>-0.0008483393660141032</v>
       </c>
       <c r="DN6" t="n">
-        <v>-0.0008540772231460187</v>
+        <v>-0.001665076037298946</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.001861435201107966</v>
+        <v>-0.004015249746190918</v>
       </c>
       <c r="DP6" t="n">
-        <v>-0.00134599206912423</v>
+        <v>-0.004441562035322593</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-2.314100586237877e-05</v>
+        <v>-4.458977407847953e-05</v>
       </c>
       <c r="DR6" t="n">
-        <v>-0.0001134987893462253</v>
+        <v>-0.0001857393578788002</v>
       </c>
       <c r="DS6" t="n">
-        <v>-3.039763618472302e-05</v>
+        <v>-0.0005575246536502598</v>
       </c>
       <c r="DT6" t="n">
-        <v>-0.0007689576717443691</v>
+        <v>-0.001712439290879586</v>
       </c>
       <c r="DU6" t="n">
-        <v>-0.001797777198464226</v>
+        <v>-0.00309795774053748</v>
       </c>
       <c r="DV6" t="n">
         <v>0</v>
       </c>
       <c r="DW6" t="n">
-        <v>-9.947910973113762e-05</v>
+        <v>-0.0001927598048164392</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.000385871334272897</v>
+        <v>-0.001056507270641038</v>
       </c>
       <c r="DY6" t="n">
-        <v>-0.0007486037890490821</v>
+        <v>-0.001526296326177476</v>
       </c>
       <c r="DZ6" t="n">
-        <v>-0.0001275745637838832</v>
+        <v>-5.394837173701706e-05</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.001517582588550256</v>
+        <v>-0.0002972661608286575</v>
       </c>
       <c r="EB6" t="n">
-        <v>-0.001739669413522757</v>
+        <v>-0.00410612237705193</v>
       </c>
       <c r="EC6" t="n">
-        <v>-0.0001713969292992362</v>
+        <v>-0.0005751501836233075</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0.0004690605629990935</v>
+        <v>-0.001434498787048277</v>
       </c>
       <c r="EE6" t="n">
-        <v>-8.326672684688675e-18</v>
+        <v>0</v>
       </c>
       <c r="EF6" t="n">
-        <v>-0.0009212356574406083</v>
+        <v>-0.0009528008443892454</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.0001050182256689181</v>
+        <v>-0.001564774087650056</v>
       </c>
       <c r="EH6" t="n">
-        <v>-0.0003442258020533107</v>
+        <v>-0.0004938719901558724</v>
       </c>
       <c r="EI6" t="n">
-        <v>-0.0006021872142907003</v>
+        <v>-0.0009204403608087581</v>
       </c>
       <c r="EJ6" t="n">
-        <v>-0.000297335906623597</v>
+        <v>-0.0002838979656400232</v>
       </c>
       <c r="EK6" t="n">
-        <v>-0.001199972211169853</v>
+        <v>-0.001660786267230638</v>
       </c>
       <c r="EL6" t="n">
-        <v>-2.31410058623871e-05</v>
+        <v>0</v>
       </c>
       <c r="EM6" t="n">
-        <v>-8.455618949999299e-05</v>
+        <v>-0.0001189325820647957</v>
       </c>
       <c r="EN6" t="n">
-        <v>-0.0003075352698931971</v>
+        <v>-0.0004252113433127702</v>
       </c>
       <c r="EO6" t="n">
         <v>0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.000301114931060692</v>
+        <v>-0.0001976209704429771</v>
       </c>
       <c r="EQ6" t="n">
-        <v>-0.001537609914617002</v>
+        <v>-0.0008198387712518074</v>
       </c>
       <c r="ER6" t="n">
-        <v>-4.46030330062519e-05</v>
+        <v>-7.431415235464034e-05</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0.0001872946902240852</v>
+        <v>-0.0001565138570775615</v>
       </c>
       <c r="ET6" t="n">
-        <v>-0.0001724109524019329</v>
+        <v>-0.001052148996356841</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0.0003696883904958287</v>
+        <v>-0.0004162735458742378</v>
       </c>
       <c r="EV6" t="n">
-        <v>-0.0001301285720968049</v>
+        <v>-0.0002671599945398118</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0.0009950883068431478</v>
+        <v>-0.001547420555975099</v>
       </c>
       <c r="EX6" t="n">
-        <v>-0.000785681221759596</v>
+        <v>-0.000712756421066732</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.0005506567949601915</v>
+        <v>-0.0007831378183636162</v>
       </c>
     </row>
     <row r="7">
@@ -3552,466 +3552,466 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0006159466462766994</v>
+        <v>-0.001082286591103415</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.0002611204710131043</v>
+        <v>-5.936492743348621e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0002824372596376967</v>
+        <v>-0.0003292066643291625</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0005704183658595818</v>
+        <v>-0.0005260170781415218</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0006156173225462192</v>
+        <v>0.000384596189125136</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001321225246863289</v>
+        <v>0.0008668326039202867</v>
       </c>
       <c r="H7" t="n">
-        <v>0.000312495299339871</v>
+        <v>0.0003227578189714142</v>
       </c>
       <c r="I7" t="n">
-        <v>4.852607726590354e-05</v>
+        <v>-0.0009560575589678156</v>
       </c>
       <c r="J7" t="n">
-        <v>-3.079733231383109e-05</v>
+        <v>-1.22407605416097e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.981787869855145e-05</v>
+        <v>-1.49655791679193e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001362714171177504</v>
+        <v>9.395657358776677e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0006309204807184055</v>
+        <v>0.0008894129956883212</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0008591846143713334</v>
+        <v>0.001965194032944428</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.000361599741014379</v>
+        <v>-0.0002675764088122756</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0003731162677802768</v>
+        <v>-0.0005168050267811752</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0002034885792315589</v>
+        <v>0.0002821921712087338</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.0005873446279368366</v>
+        <v>-0.0006531599058832605</v>
       </c>
       <c r="S7" t="n">
-        <v>0.00115517501323858</v>
+        <v>0.0006457905174520162</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0001084591219724096</v>
+        <v>-0.0001368930576509164</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0004464790259226525</v>
+        <v>-0.0005851759222418096</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.0002253022566527707</v>
+        <v>0.0003267273625619738</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.001999971425600427</v>
+        <v>-0.001135198376768637</v>
       </c>
       <c r="X7" t="n">
-        <v>0.001255154241135786</v>
+        <v>-0.0007908910855596141</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.152011453224859e-05</v>
+        <v>-4.477158329397879e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.003380135967967263</v>
+        <v>0.002481941280754213</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.001103726345176742</v>
+        <v>-0.0003663252792004801</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0004809858887277696</v>
+        <v>-5.893880052428302e-05</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.0007024258630963176</v>
+        <v>-0.0005077799978694952</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.005971569356403817</v>
+        <v>0.002105349281842161</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.001140233093425108</v>
+        <v>0.004854274880793624</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.001045724489695904</v>
+        <v>0.0002445892386792992</v>
       </c>
       <c r="AG7" t="n">
-        <v>-3.057082283199342e-05</v>
+        <v>-0.0001164763268093616</v>
       </c>
       <c r="AH7" t="n">
-        <v>-1.171727263396538e-05</v>
+        <v>0.0001103193768684174</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.0004840385053658969</v>
+        <v>0.0008844316100647843</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.0004765631808338222</v>
+        <v>3.353684818658826e-05</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.01301260057213098</v>
+        <v>0.009241125000765665</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.0006428772366953994</v>
+        <v>7.575047827757531e-05</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.001422478063187954</v>
+        <v>0.001064770121321068</v>
       </c>
       <c r="AN7" t="n">
-        <v>-4.684572142411025e-05</v>
+        <v>-0.001273731940757161</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.0001260493431962828</v>
+        <v>-0.0005451002712742181</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.0004164783023379859</v>
+        <v>-0.0005568115009293938</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.0003091204887551879</v>
+        <v>-0.000227312395684498</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.001148464783873776</v>
+        <v>0.001484692235357676</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0.0002105499656717857</v>
+        <v>3.732966688030912e-05</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.720731004296038e-05</v>
+        <v>-0.0004265728258901592</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.00010447738321126</v>
+        <v>-0.0003475248936578357</v>
       </c>
       <c r="AV7" t="n">
-        <v>-0.0001785664660778008</v>
+        <v>-0.0001690027035556929</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.0005848527523824809</v>
+        <v>1.429768504157544e-06</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.0001394097448736642</v>
+        <v>0.000188974955264698</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.001356451885618615</v>
+        <v>-0.001490977531338933</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.0003566855509151701</v>
+        <v>-8.825117476370938e-05</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.002478379523990404</v>
+        <v>-0.0001004683849226695</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.001404276092669132</v>
+        <v>-0.002939153147239482</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.0001203535112837995</v>
+        <v>3.272560656132352e-05</v>
       </c>
       <c r="BD7" t="n">
-        <v>-7.060057431397814e-05</v>
+        <v>-4.646508937989347e-05</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.0004236368799079738</v>
+        <v>-0.0005465447536494805</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.0006495732086332028</v>
+        <v>-0.00189008258878684</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.001137243940909216</v>
+        <v>-0.0001854612037208492</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.0002084934940094207</v>
+        <v>-0.0002672304222120558</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.003906454832995515</v>
+        <v>0.001141379825079808</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.0007080172420894593</v>
+        <v>0.0003409366452163165</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.000209211144925503</v>
+        <v>-0.0003298120726526743</v>
       </c>
       <c r="BL7" t="n">
-        <v>-4.479441636200954e-05</v>
+        <v>-0.0003864703357736587</v>
       </c>
       <c r="BM7" t="n">
-        <v>-0.0005003516795461293</v>
+        <v>-0.0002190605924468736</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.001318324686678307</v>
+        <v>-0.002102993508609879</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.001745053024141369</v>
+        <v>-0.0006976175229549853</v>
       </c>
       <c r="BP7" t="n">
-        <v>-0.0005648700996329304</v>
+        <v>-0.0004815121607105899</v>
       </c>
       <c r="BQ7" t="n">
         <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-1.557814227828303e-05</v>
+        <v>0.001054057854460916</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.0001555027434402445</v>
+        <v>-0.0005814095943278197</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.0003283729567996052</v>
+        <v>0.0001971511744100374</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.0008898574374828216</v>
+        <v>0.001310384160296163</v>
       </c>
       <c r="BV7" t="n">
-        <v>-0.001216936960050541</v>
+        <v>-0.00110822267921179</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.481920569057493e-05</v>
+        <v>-3.026634382566895e-05</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.0001309961479218136</v>
+        <v>-0.0004869748766312632</v>
       </c>
       <c r="BY7" t="n">
-        <v>-0.0002181922218167709</v>
+        <v>-0.0003026700714669817</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0.0008380490642914184</v>
+        <v>0.0002872647720997601</v>
       </c>
       <c r="CA7" t="n">
-        <v>-1.496462162511313e-05</v>
+        <v>0.0002758323365442073</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0.0001345790638954458</v>
+        <v>0.0005998064186176378</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.0003721904952774746</v>
+        <v>-0.0006688416885794024</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.0008725285958518403</v>
+        <v>7.458060414426427e-05</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.000282401902496987</v>
+        <v>-0.0008394909256902229</v>
       </c>
       <c r="CF7" t="n">
-        <v>-0.0002086659083349041</v>
+        <v>-0.001432715456919337</v>
       </c>
       <c r="CG7" t="n">
-        <v>7.610350076100447e-05</v>
+        <v>-0.0003946343247586804</v>
       </c>
       <c r="CH7" t="n">
-        <v>9.51092138119003e-05</v>
+        <v>-0.0005119284557321192</v>
       </c>
       <c r="CI7" t="n">
-        <v>-0.0005546523909618962</v>
+        <v>-0.0008120331786823144</v>
       </c>
       <c r="CJ7" t="n">
         <v>0</v>
       </c>
       <c r="CK7" t="n">
-        <v>-1.627164402129289e-05</v>
+        <v>-7.050142811515503e-05</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.0005082485205911757</v>
+        <v>-0.001029665093333754</v>
       </c>
       <c r="CM7" t="n">
-        <v>1.620822112602394e-05</v>
+        <v>0.0004727927179876024</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.0002046766082318186</v>
+        <v>-0.0001038798557685183</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.0004427185339671347</v>
+        <v>-0.0001554007918145639</v>
       </c>
       <c r="CP7" t="n">
-        <v>4.574893751962961e-05</v>
+        <v>0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.0006169815668335132</v>
+        <v>-0.0004667713481033675</v>
       </c>
       <c r="CR7" t="n">
-        <v>-0.001247305636426643</v>
+        <v>-0.001691548013169203</v>
       </c>
       <c r="CS7" t="n">
-        <v>-0.0005136225798234139</v>
+        <v>-0.00143649474016333</v>
       </c>
       <c r="CT7" t="n">
-        <v>-7.14884252117634e-07</v>
+        <v>-0.0001802723014480645</v>
       </c>
       <c r="CU7" t="n">
-        <v>4.609277729065165e-05</v>
+        <v>-0.0002922678526366851</v>
       </c>
       <c r="CV7" t="n">
-        <v>0</v>
+        <v>-2.993115833582749e-05</v>
       </c>
       <c r="CW7" t="n">
         <v>0</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0.0003919113891929893</v>
+        <v>-0.0003929318731301701</v>
       </c>
       <c r="CY7" t="n">
-        <v>-7.847074269601295e-05</v>
+        <v>-0.001702273182270692</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.0001061317515015425</v>
+        <v>3.123048094940684e-05</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.0001193566344478647</v>
+        <v>2.775557561562891e-17</v>
       </c>
       <c r="DB7" t="n">
-        <v>-0.0002283816553594442</v>
+        <v>-0.0003921299656997057</v>
       </c>
       <c r="DC7" t="n">
-        <v>-1.02702866791593e-05</v>
+        <v>0.0003570180929976963</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.0001067080380957652</v>
+        <v>-9.177228040253561e-05</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.0006579574206798999</v>
+        <v>0.0001568020660538239</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.000717916659269524</v>
+        <v>-0.0007653229587134769</v>
       </c>
       <c r="DG7" t="n">
-        <v>6.17093489663767e-05</v>
+        <v>-0.0001652830489180357</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.0002701457879753288</v>
+        <v>-0.001595984250024374</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.000394542605966175</v>
+        <v>-0.0005986384014761537</v>
       </c>
       <c r="DJ7" t="n">
-        <v>6.321294434732949e-05</v>
+        <v>-0.0001517693603252102</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.0002586021830812246</v>
+        <v>-0.000325355762732743</v>
       </c>
       <c r="DL7" t="n">
+        <v>-1.496557916791375e-05</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>-0.0002827088659222987</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>-1.798248240970633e-05</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>-0.001194369333401924</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>-0.00108376309465229</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>3.039291640950514e-05</v>
+      </c>
+      <c r="DR7" t="n">
         <v>0</v>
-      </c>
-      <c r="DM7" t="n">
-        <v>0.0004083347829888451</v>
-      </c>
-      <c r="DN7" t="n">
-        <v>2.901163180019649e-05</v>
-      </c>
-      <c r="DO7" t="n">
-        <v>-0.0001223232785704686</v>
-      </c>
-      <c r="DP7" t="n">
-        <v>-0.0005121462645048924</v>
-      </c>
-      <c r="DQ7" t="n">
-        <v>1.496557916791375e-05</v>
-      </c>
-      <c r="DR7" t="n">
-        <v>1.561524047470342e-05</v>
       </c>
       <c r="DS7" t="n">
         <v>0</v>
       </c>
       <c r="DT7" t="n">
-        <v>-7.520842264486239e-05</v>
+        <v>-0.0005066758587274067</v>
       </c>
       <c r="DU7" t="n">
-        <v>-0.001124344052402149</v>
+        <v>-0.0001322518174999232</v>
       </c>
       <c r="DV7" t="n">
         <v>0</v>
       </c>
       <c r="DW7" t="n">
-        <v>-1.481920569057493e-05</v>
+        <v>0.0001095092220320226</v>
       </c>
       <c r="DX7" t="n">
-        <v>-2.963841138115542e-05</v>
+        <v>4.418048951142507e-05</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.000965665475458366</v>
+        <v>-0.0006225608238149937</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.000103910649176342</v>
+        <v>-2.982883719407359e-05</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.0002830732847012351</v>
+        <v>0.0001186858025313264</v>
       </c>
       <c r="EB7" t="n">
-        <v>-9.207113317543644e-05</v>
+        <v>-0.000521501653906209</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.0001545742434570507</v>
+        <v>-4.177300208823564e-05</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0.0002559231805587814</v>
+        <v>-0.0006983294448527078</v>
       </c>
       <c r="EE7" t="n">
         <v>0</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.0001555027434402445</v>
+        <v>-0.0001272268407413957</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.0004220976685131106</v>
+        <v>-0.0008411728340192382</v>
       </c>
       <c r="EH7" t="n">
-        <v>-0.0001634958382877638</v>
+        <v>1.481920569057493e-05</v>
       </c>
       <c r="EI7" t="n">
-        <v>-0.0002290313166662339</v>
+        <v>-0.0002495704894609485</v>
       </c>
       <c r="EJ7" t="n">
-        <v>-0.0002286563636316519</v>
+        <v>-0.0002237674395264344</v>
       </c>
       <c r="EK7" t="n">
-        <v>-0.0002299908003679796</v>
+        <v>-0.0003989109390831469</v>
       </c>
       <c r="EL7" t="n">
         <v>0</v>
       </c>
       <c r="EM7" t="n">
-        <v>0</v>
+        <v>-3.009875108074822e-05</v>
       </c>
       <c r="EN7" t="n">
-        <v>-1.101422569849136e-06</v>
+        <v>-0.0001049266469203169</v>
       </c>
       <c r="EO7" t="n">
         <v>0</v>
       </c>
       <c r="EP7" t="n">
-        <v>2.973535533746796e-05</v>
+        <v>7.703074097929474e-05</v>
       </c>
       <c r="EQ7" t="n">
-        <v>-0.0003340155728301375</v>
+        <v>-0.0001493828216543924</v>
       </c>
       <c r="ER7" t="n">
         <v>0</v>
       </c>
       <c r="ES7" t="n">
-        <v>-1.522070015220756e-05</v>
+        <v>-7.559325879245016e-05</v>
       </c>
       <c r="ET7" t="n">
-        <v>7.441861127253092e-05</v>
+        <v>-0.0004098444878151919</v>
       </c>
       <c r="EU7" t="n">
-        <v>9.144875443032885e-05</v>
+        <v>0.0002006308842361582</v>
       </c>
       <c r="EV7" t="n">
-        <v>-4.55442952361329e-05</v>
+        <v>-0.0001198095104136321</v>
       </c>
       <c r="EW7" t="n">
-        <v>9.448052349321224e-05</v>
+        <v>-0.0004388619854721554</v>
       </c>
       <c r="EX7" t="n">
-        <v>-9.228017179835346e-05</v>
+        <v>-0.0005533340701073918</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.0001541747615958267</v>
+        <v>-4.464161651944742e-05</v>
       </c>
     </row>
     <row r="8">
@@ -4021,466 +4021,466 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002984565189534843</v>
+        <v>0.001520938833069149</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0006681368013386508</v>
+        <v>0.0002046550245339146</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0005341109642104879</v>
+        <v>0.0002560758756714326</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001036898886409399</v>
+        <v>0.0006072551507608215</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0009156790844449176</v>
+        <v>0.001030540695222126</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002396675584935587</v>
+        <v>0.002280349551251742</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001349685847642248</v>
+        <v>0.001275509290912435</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001956944499821991</v>
+        <v>0.001017194250795142</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0003288716326968338</v>
+        <v>0.001944618124632874</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0003712851963897368</v>
+        <v>0.0001952917752883421</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0002946811753591044</v>
+        <v>0.0003735767129181749</v>
       </c>
       <c r="M8" t="n">
-        <v>0.00148833419086144</v>
+        <v>0.001398228006841568</v>
       </c>
       <c r="N8" t="n">
-        <v>0.004304364485250553</v>
+        <v>0.004981738779484402</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001082394159890712</v>
+        <v>0.0006457332486200507</v>
       </c>
       <c r="P8" t="n">
-        <v>0.001146611724611132</v>
+        <v>2.177198277795722e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.007625288912035988</v>
+        <v>0.004688212546528032</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0002525872817734975</v>
+        <v>0.0001487498619278799</v>
       </c>
       <c r="S8" t="n">
-        <v>0.002753428206815339</v>
+        <v>0.001809903817724268</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0009572150647628479</v>
+        <v>8.410839115961245e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.000219653144846324</v>
+        <v>-0.0003245035627168658</v>
       </c>
       <c r="V8" t="n">
-        <v>0.001130132232803513</v>
+        <v>0.001844841274842135</v>
       </c>
       <c r="W8" t="n">
-        <v>-8.677530264866176e-05</v>
+        <v>0.0006858505533627046</v>
       </c>
       <c r="X8" t="n">
-        <v>0.004919128580470849</v>
+        <v>0.0002057440265088722</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0001413331017477676</v>
+        <v>0.0001495871014191907</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.005982578033595944</v>
+        <v>0.004790250722013329</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.002389724410518693</v>
+        <v>0.003018433114006922</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0006226052189814729</v>
+        <v>0.0005573516078037994</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.002105626751961393</v>
+        <v>-9.399525091187411e-05</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.008338344640834376</v>
+        <v>0.00588968517483592</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.01114882075308244</v>
+        <v>0.01196235712215349</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.003628931788999959</v>
+        <v>0.001184082181448973</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0002082902546496873</v>
+        <v>0.001029493331269513</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0005120497359282521</v>
+        <v>0.0004018272481368851</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.001857498172773733</v>
+        <v>0.002643276817731191</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.00297868358498998</v>
+        <v>0.002267546137250604</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.01636790807293966</v>
+        <v>0.01398045813327282</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.001663189383828415</v>
+        <v>0.0002826662034955296</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.00268303172134205</v>
+        <v>0.007008575427601313</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.001992856774317197</v>
+        <v>0.0004962509162366707</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.003511542163650671</v>
+        <v>0.0006337421979205254</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.001251169401817856</v>
+        <v>-0.0002417289200547956</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.001579668681356841</v>
+        <v>0.001476353875377534</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.00620815638741427</v>
+        <v>0.007709719450513361</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.001457012476544159</v>
+        <v>0.001420358181044604</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.00113573447929661</v>
+        <v>0.0008711492729788135</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.001015622191663587</v>
+        <v>0.0003423301190388</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.0003490442757689977</v>
+        <v>0.000362731659611562</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.001255288223400525</v>
+        <v>0.0003707467381443341</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.0004169918166719272</v>
+        <v>0.0006365885904472651</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.003469946693801909</v>
+        <v>0.0003767571323213787</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.0009779820174938253</v>
+        <v>0.0009691326455136123</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.005708270956165945</v>
+        <v>0.0011503011667999</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.003249206866050464</v>
+        <v>0.001860267761412956</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.0002173971975006184</v>
+        <v>0.0002197512015157971</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.0002671848228623652</v>
+        <v>0.0001579752531289141</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.001438236262910866</v>
+        <v>0.000158426219320798</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.003136217802874331</v>
+        <v>-0.000202445744002161</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.0001873410964712136</v>
+        <v>0.000148665727581021</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.0009804282054345942</v>
+        <v>0.0005992474229825628</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.00876720475439817</v>
+        <v>0.004925212587742551</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.001893571874829031</v>
+        <v>0.001599844231143832</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.0009931084990767143</v>
+        <v>0.0004909270675662104</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.0002311029188196229</v>
+        <v>0.0004514143228656564</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.001021489104116258</v>
+        <v>0.000252858826839969</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.004403873024267688</v>
+        <v>0.001130215419016084</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.00258419295277898</v>
+        <v>0.001223287043602478</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.0002039843026872046</v>
+        <v>-0.0002912956063341798</v>
       </c>
       <c r="BQ8" t="n">
         <v>0</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.001668094870754416</v>
+        <v>0.003653014632268805</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.001720819174525684</v>
+        <v>-0.0001046032774064343</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.0007416357270760316</v>
+        <v>0.001158519225414303</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.001454145771276938</v>
+        <v>0.001972578182443235</v>
       </c>
       <c r="BV8" t="n">
-        <v>-0.0001298060681544255</v>
+        <v>-4.599816007359869e-05</v>
       </c>
       <c r="BW8" t="n">
-        <v>5.249866367036393e-05</v>
+        <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.0008676525189311558</v>
+        <v>0.0001939743367885716</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.002726243267489575</v>
+        <v>0.0003651685085985595</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0.0004055331246916816</v>
+        <v>0.0007993342573075046</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.0007210265703949392</v>
+        <v>0.000432492688185937</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.0004532594163322689</v>
+        <v>0.001626269860876439</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.001161561086854762</v>
+        <v>0.0004841075083834328</v>
       </c>
       <c r="CD8" t="n">
-        <v>0.002450095140653879</v>
+        <v>0.0007752053688900501</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.0007171379284022367</v>
+        <v>0.0005640976410096921</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.001120548885579692</v>
+        <v>-0.0002944476949253511</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.001062757346012622</v>
+        <v>0.0004581084510192679</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.0005164833212378734</v>
+        <v>7.118000632710397e-05</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.0003566757888513544</v>
+        <v>-0.0007140347210905617</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0</v>
+        <v>3.010936071453918e-05</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.001161800608843333</v>
+        <v>0.0009666645427127279</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.00081103705161443</v>
+        <v>-1.533272002452179e-05</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.001424703742443875</v>
+        <v>0.0008434210251073382</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.00062023142767543</v>
+        <v>0.0002751562237071986</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.001094712583755075</v>
+        <v>0.0007568570622216913</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.0004328216933887907</v>
+        <v>0.0001112167506465783</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.001259301232534787</v>
+        <v>0.0001060891865009628</v>
       </c>
       <c r="CR8" t="n">
-        <v>-0.0004438277436624366</v>
+        <v>0.0005971359319143305</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.0003325874784468802</v>
+        <v>0.0008707217963218633</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.0005610212376906704</v>
+        <v>0.0001440864094773592</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.0003644539058826251</v>
+        <v>-0.0001395097081090479</v>
       </c>
       <c r="CV8" t="n">
-        <v>8.316288543941397e-05</v>
+        <v>0.0001443534638294469</v>
       </c>
       <c r="CW8" t="n">
         <v>0</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.0006768748562972133</v>
+        <v>0.0002601321343691898</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.0001764208974991882</v>
+        <v>0.001496161221875555</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.0005184222702665081</v>
+        <v>0.0001585000637186168</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.0004528653428781504</v>
+        <v>0.000404794395680394</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.001438846055817483</v>
+        <v>0.0004356728708157675</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.000923563019783355</v>
+        <v>0.0008695781832561173</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.0002404902740424208</v>
+        <v>0.0001074272814757027</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.0009955087402324704</v>
+        <v>0.0008767530152380575</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.001041268239752014</v>
+        <v>0.001281086368393489</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.0008718953037416544</v>
+        <v>5.28333545728954e-05</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.003169727259709612</v>
+        <v>0.0006500578667911789</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.001164078248079206</v>
+        <v>0.0003722562353706215</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.0008360232047204263</v>
+        <v>0.00078503845444505</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.001142176269807687</v>
+        <v>0.0003532176014646226</v>
       </c>
       <c r="DL8" t="n">
-        <v>4.458977407846287e-05</v>
+        <v>0.0001187543927554158</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.0007798065706650398</v>
+        <v>0.0009516882998353933</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.0004739385676101992</v>
+        <v>0.0009881061215954389</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.0001191881038169668</v>
+        <v>-9.429905897551661e-05</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.0009516298565706016</v>
+        <v>0.0001079901817137796</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.0001179057551396079</v>
+        <v>0.0001061918785819988</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.0001958131974822308</v>
+        <v>2.988220758624871e-05</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.0003345227475467977</v>
+        <v>0</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.0004838504491775474</v>
+        <v>0.0006313254652824729</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.0004696434418652528</v>
+        <v>0.00157992669291151</v>
       </c>
       <c r="DV8" t="n">
         <v>0</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.0001975270188264239</v>
+        <v>0.0003924672327583839</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.001063237626136978</v>
+        <v>0.0003401530322475005</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.001427197614241516</v>
+        <v>0.00159457932458584</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.0001910478325475862</v>
+        <v>8.92060660125038e-05</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.0003821974004059536</v>
+        <v>0.0006224747008820253</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.0004922219642442105</v>
+        <v>0.00079908675799083</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.0005438740501402251</v>
+        <v>0.0005150326477908057</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.0003269476242398733</v>
+        <v>-0.0004295116752385419</v>
       </c>
       <c r="EE8" t="n">
-        <v>4.460303300623524e-05</v>
+        <v>4.62820117247742e-05</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.0007471025359898713</v>
+        <v>3.108922072432852e-05</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.0009038066300943393</v>
+        <v>-0.0003614699888885742</v>
       </c>
       <c r="EH8" t="n">
-        <v>0</v>
+        <v>0.0003059559820997343</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.0002527549400112572</v>
+        <v>0.0002479155733477761</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.0003105801371706129</v>
+        <v>0.000307219441391024</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.0006173879743652049</v>
+        <v>3.108922072433129e-05</v>
       </c>
       <c r="EL8" t="n">
         <v>0</v>
       </c>
       <c r="EM8" t="n">
-        <v>2.244836875187062e-05</v>
+        <v>2.342286071205513e-05</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.0001505468035726959</v>
+        <v>0.000154461275649026</v>
       </c>
       <c r="EO8" t="n">
         <v>0</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.0002510102601523651</v>
+        <v>0.0004647095533189122</v>
       </c>
       <c r="EQ8" t="n">
-        <v>5.940897976901283e-05</v>
+        <v>0.0001299609793519229</v>
       </c>
       <c r="ER8" t="n">
         <v>0</v>
       </c>
       <c r="ES8" t="n">
-        <v>2.314100586239542e-05</v>
+        <v>3.749062614660236e-05</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.0002975929134110184</v>
+        <v>0.0001559637632731287</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.0003039037610755635</v>
+        <v>0.000567097398963623</v>
       </c>
       <c r="EV8" t="n">
-        <v>5.445607150021404e-05</v>
+        <v>-1.522070015220756e-05</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.0006327989209608976</v>
+        <v>7.64288691235071e-05</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.00022239901008827</v>
+        <v>-0.0003774880235271227</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.000365296803652973</v>
+        <v>7.471216974674621e-05</v>
       </c>
     </row>
     <row r="9">
@@ -4490,466 +4490,466 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.007699167657550488</v>
+        <v>0.00301369863013694</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001126259632483695</v>
+        <v>0.0009987893462469755</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00334914048606999</v>
+        <v>0.001502606562404218</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00257854179016006</v>
+        <v>0.001066982809721395</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001516503122212265</v>
+        <v>0.001851280468991079</v>
       </c>
       <c r="G9" t="n">
-        <v>0.004176755447941949</v>
+        <v>0.00338983050847459</v>
       </c>
       <c r="H9" t="n">
-        <v>0.002334630350194544</v>
+        <v>0.002373516552154919</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002459988144635472</v>
+        <v>0.002309395760835142</v>
       </c>
       <c r="J9" t="n">
-        <v>0.003805175038051745</v>
+        <v>0.002705917335712194</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0008474576271187084</v>
+        <v>0.000705305121128541</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001876513317191342</v>
+        <v>0.000726392251815966</v>
       </c>
       <c r="M9" t="n">
-        <v>0.002300242130750652</v>
+        <v>0.003416640303701324</v>
       </c>
       <c r="N9" t="n">
-        <v>0.008977407847800179</v>
+        <v>0.006327111673521013</v>
       </c>
       <c r="O9" t="n">
-        <v>0.003068649161657666</v>
+        <v>0.001550142360012618</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001511558980438643</v>
+        <v>0.0001778304682868992</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.02085351089588382</v>
+        <v>0.01934019370460048</v>
       </c>
       <c r="R9" t="n">
-        <v>0.001613394216133923</v>
+        <v>0.001573588398642423</v>
       </c>
       <c r="S9" t="n">
-        <v>0.003342532965348044</v>
+        <v>0.004354492486967232</v>
       </c>
       <c r="T9" t="n">
-        <v>0.001452784503632021</v>
+        <v>0.0007566585956416572</v>
       </c>
       <c r="U9" t="n">
-        <v>0.001187214611872134</v>
+        <v>0.001471941122355136</v>
       </c>
       <c r="V9" t="n">
-        <v>0.006807727690892362</v>
+        <v>0.003638089212274576</v>
       </c>
       <c r="W9" t="n">
-        <v>0.001367419738406617</v>
+        <v>0.001686599202698591</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01073446327683614</v>
+        <v>0.005322628605411861</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0005927682276229973</v>
+        <v>0.0006839131727624404</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.0111380145278451</v>
+        <v>0.007529262891489997</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.01070154577883466</v>
+        <v>0.005985806849737774</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.001185536455245995</v>
+        <v>0.002845036319612604</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.003208886146251211</v>
+        <v>0.004748858447488536</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.01579759333539036</v>
+        <v>0.0142857142857143</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.02106544901065448</v>
+        <v>0.02184510953409444</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.008608454180808434</v>
+        <v>0.003622735790131193</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.003813559322033955</v>
+        <v>0.001727861771058348</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.002039573820395713</v>
+        <v>0.001758716445541531</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.005917335712161719</v>
+        <v>0.008652988403211459</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.01729071537290714</v>
+        <v>0.006210045662100416</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.03532560214094554</v>
+        <v>0.04311626523936964</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.003716919417186992</v>
+        <v>0.003054612773835286</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.01576864535768645</v>
+        <v>0.01363774733637744</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.002221536562789306</v>
+        <v>0.002118644067796605</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.006567796610169541</v>
+        <v>0.01005055010407377</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.002931194075902554</v>
+        <v>0.002841973766396022</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.004751619870410428</v>
+        <v>0.00465753424657529</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.01172477630361004</v>
+        <v>0.01481024375192845</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.003360095153137033</v>
+        <v>0.005947071067499266</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.001664684898929791</v>
+        <v>0.002349093071662256</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.004252155813261915</v>
+        <v>0.001974699166923821</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.003934624697336608</v>
+        <v>0.00136986301369858</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.003450363196125939</v>
+        <v>0.001311680199875087</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.001278620279512299</v>
+        <v>0.001851280468991079</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.004176755447941926</v>
+        <v>0.001993040177159078</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.002784503631961322</v>
+        <v>0.001202151217968961</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.00906658739595716</v>
+        <v>0.01183467142432356</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.008645357686453548</v>
+        <v>0.01153729071537287</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.0009187907528156458</v>
+        <v>0.0003957382039573521</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.0006479481641469165</v>
+        <v>0.0009079903147699686</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.004965804341361846</v>
+        <v>0.002795123401724686</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.008474576271186396</v>
+        <v>0.01465953018138572</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.009928656361474376</v>
+        <v>0.0008002371072910464</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.004430567945286901</v>
+        <v>0.002815564694716821</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.01343638525564798</v>
+        <v>0.02106544901065445</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.00521443998765817</v>
+        <v>0.005235920852359177</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.006095747844186717</v>
+        <v>0.001561524047470342</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.0009873495834619383</v>
+        <v>0.000756658595641635</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.001491628614916285</v>
+        <v>0.001180387409200967</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.00717571297148113</v>
+        <v>0.004757656853999437</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.005677764565992805</v>
+        <v>0.002039573820395701</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.002283245911755672</v>
+        <v>0</v>
       </c>
       <c r="BQ9" t="n">
         <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.01198334820101095</v>
+        <v>0.03832887303003273</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.003865596193874465</v>
+        <v>0.002966101694915247</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.001203332304844229</v>
+        <v>0.003033006244424641</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.009099018733273822</v>
+        <v>0.003449301219149603</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.00185128046899109</v>
+        <v>0.0004684572142411025</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.0003652968036529813</v>
+        <v>3.044140030441511e-05</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.001575505350772832</v>
+        <v>0.003158540325053716</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.004965804341361835</v>
+        <v>0.006355932203389836</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.004751815980629581</v>
+        <v>0.003835616438356127</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.004011107682814008</v>
+        <v>0.00136782634552487</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.00243593799430557</v>
+        <v>0.002451573849878941</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.002845036319612659</v>
+        <v>0.001704718417047157</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.005305121128488188</v>
+        <v>0.002869484726936144</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.004165381055229911</v>
+        <v>0.004782474544893589</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.001796042617960414</v>
+        <v>0.0006697108066970548</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.001727861771058359</v>
+        <v>0.002283245911755649</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.0009812667261373197</v>
+        <v>0.001079913606911509</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.00136782634552477</v>
+        <v>0.0002186133666458478</v>
       </c>
       <c r="CJ9" t="n">
-        <v>8.89152341434496e-05</v>
+        <v>5.945303210461716e-05</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.003394014193150308</v>
+        <v>0.003579142240049404</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.002170680939637182</v>
+        <v>0.003238498789346256</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.004936068986024356</v>
+        <v>0.002111210228962279</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.002497769848349651</v>
+        <v>0.00236123888377805</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.007166220636336562</v>
+        <v>0.002118644067796605</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.0008432229856339846</v>
+        <v>0.0002130898021308947</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.00793933987511145</v>
+        <v>0.0005933791380387299</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.002406664609688414</v>
+        <v>0.001905059337913817</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.002009132420091286</v>
+        <v>0.00128044971892568</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.002119582410629495</v>
+        <v>0.0002847200253084381</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.001089588377724016</v>
+        <v>-3.123048094940684e-05</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.0003934624697336964</v>
+        <v>0.0003796267004112508</v>
       </c>
       <c r="CW9" t="n">
         <v>0</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.00354828756556621</v>
+        <v>0.0004906470407850749</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.001129607609988048</v>
+        <v>0.002578541790160038</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.000852359208523601</v>
+        <v>0.0003591739000299299</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.001308355634849789</v>
+        <v>0.001248097412480908</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.002021403091557628</v>
+        <v>0.002602905569007286</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.002557077625570758</v>
+        <v>0.00187382885696441</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.0005927682276229973</v>
+        <v>0.0001815980629539804</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.001338090990187291</v>
+        <v>0.002996368038740926</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.004504782474544933</v>
+        <v>0.002313546423135427</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.001218787158145007</v>
+        <v>0.000749531542785764</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.004388619854721609</v>
+        <v>0.004412218451095374</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.002051129607609947</v>
+        <v>0.002343987823439842</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.002422569763876103</v>
+        <v>0.001042624961668237</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.001856925418569233</v>
+        <v>0.0006088280060882467</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.0004011107682814208</v>
+        <v>0.0003329297820823252</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.001486767766874752</v>
+        <v>0.002996368038740926</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.002838630052452995</v>
+        <v>0.004227090404196276</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.0008219178082191636</v>
+        <v>0.002875302663438262</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.003359564164648965</v>
+        <v>0.002693704600484259</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.0007566585956416905</v>
+        <v>0.001073290401717297</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.00120333230484424</v>
+        <v>0.0002468373958654624</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.001155898043864845</v>
+        <v>9.49066751028127e-05</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.00308546744831848</v>
+        <v>0.005447941888619845</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.004350509102129007</v>
+        <v>0.002992903424868909</v>
       </c>
       <c r="DV9" t="n">
-        <v>2.973535533749016e-05</v>
+        <v>0</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.0005145278450363611</v>
+        <v>0.00133171912832929</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.002319357716324688</v>
+        <v>0.001304090100770594</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.005677260104905946</v>
+        <v>0.003980253008330792</v>
       </c>
       <c r="DZ9" t="n">
         <v>0.0003796267004112508</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.001226617601962598</v>
+        <v>0.001754385964912342</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.00509102128972545</v>
+        <v>0.004196235729713083</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.002530083307621145</v>
+        <v>0.0007263922518159771</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.00249776984834964</v>
+        <v>0.0006392694063926619</v>
       </c>
       <c r="EE9" t="n">
-        <v>0.0007096575131132932</v>
+        <v>0.0002453235203925596</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.001694915254237339</v>
+        <v>0.001004566210045588</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.003687184061849502</v>
+        <v>0.0004684572142411025</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.0005334914048606976</v>
+        <v>0.0006392694063926507</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.001826484018264796</v>
+        <v>0.00167427701674272</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.00172465060957474</v>
+        <v>0.0008639308855292072</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.002633171912832988</v>
+        <v>0.0006658595641646281</v>
       </c>
       <c r="EL9" t="n">
-        <v>9.132420091324533e-05</v>
+        <v>9.199632014721404e-05</v>
       </c>
       <c r="EM9" t="n">
-        <v>5.927682276229973e-05</v>
+        <v>0.0001265422334704169</v>
       </c>
       <c r="EN9" t="n">
-        <v>0.0003865596193874165</v>
+        <v>0.0003373198405397515</v>
       </c>
       <c r="EO9" t="n">
         <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.001694411414982111</v>
+        <v>0.000761035007610289</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.001430745814307432</v>
+        <v>0.000562148657089323</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.001138880101233752</v>
+        <v>0.0005519779208831954</v>
       </c>
       <c r="ES9" t="n">
-        <v>6.053268765136011e-05</v>
+        <v>0.000187382885696441</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.001400304414003006</v>
+        <v>0.0009812940815701388</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.001483050847457679</v>
+        <v>0.001040737436812411</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.0008325899494498468</v>
+        <v>6.327111673520847e-05</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.0011972463334331</v>
+        <v>0.001012337867763335</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.000605326876513368</v>
+        <v>0.000365296803652948</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.001604116222760343</v>
+        <v>0.0006355932203389702</v>
       </c>
     </row>
   </sheetData>
